--- a/Connected Warriors Yoga Classes .xlsx
+++ b/Connected Warriors Yoga Classes .xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8193B2ED35B6ABA2/Connected Warriors/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8193b2ed35b6aba2/Connected Warriors/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="8_{2419E654-9B3A-416A-B670-D190A08224AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B99F60D-175E-484E-AFE0-E2058EFD3E4E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08605CF3-99FB-46F9-9DE3-A0F6F3E7C790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="94">
   <si>
     <t>First name</t>
   </si>
@@ -105,12 +105,6 @@
     <t>Manchester, TN</t>
   </si>
   <si>
-    <t>Hope</t>
-  </si>
-  <si>
-    <t>Weiner</t>
-  </si>
-  <si>
     <t>hopeweiner@gmail.com</t>
   </si>
   <si>
@@ -126,18 +120,6 @@
     <t>954-304-2016</t>
   </si>
   <si>
-    <t>cdrbingo@connectedwarriors.org</t>
-  </si>
-  <si>
-    <t>Anna Maria</t>
-  </si>
-  <si>
-    <t>561-843-8697</t>
-  </si>
-  <si>
-    <t>amariaaste@gmail.com</t>
-  </si>
-  <si>
     <t>Mary</t>
   </si>
   <si>
@@ -150,45 +132,6 @@
     <t>mary@connectedwarriors.org</t>
   </si>
   <si>
-    <t>Shannon</t>
-  </si>
-  <si>
-    <t>Shelley</t>
-  </si>
-  <si>
-    <t>(561) 307-2563</t>
-  </si>
-  <si>
-    <t>shannon33467@yahoo.com</t>
-  </si>
-  <si>
-    <t>Tom</t>
-  </si>
-  <si>
-    <t>Sheridan</t>
-  </si>
-  <si>
-    <t>561-693-9114</t>
-  </si>
-  <si>
-    <t>sheridantw@yahoo.com</t>
-  </si>
-  <si>
-    <t>Jim</t>
-  </si>
-  <si>
-    <t>O'Rourke</t>
-  </si>
-  <si>
-    <t>561-427-9191</t>
-  </si>
-  <si>
-    <t>val21487@aol.com</t>
-  </si>
-  <si>
-    <t>Port Saint Lucie, FL</t>
-  </si>
-  <si>
     <t>Lisa</t>
   </si>
   <si>
@@ -204,109 +147,6 @@
     <t>Miami,Fl</t>
   </si>
   <si>
-    <t>Ashley</t>
-  </si>
-  <si>
-    <t>Rush</t>
-  </si>
-  <si>
-    <t>407.222.3293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashley.Rush@va.gov </t>
-  </si>
-  <si>
-    <t>Orlando, FL</t>
-  </si>
-  <si>
-    <t>Beth</t>
-  </si>
-  <si>
-    <t>Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">561.251.8646
-</t>
-  </si>
-  <si>
-    <t>bethfjohnson33@gmail.com</t>
-  </si>
-  <si>
-    <t>Pompano, FL</t>
-  </si>
-  <si>
-    <t>Leesa</t>
-  </si>
-  <si>
-    <t>Loeffer</t>
-  </si>
-  <si>
-    <t>leesaloeffer@gmail.com</t>
-  </si>
-  <si>
-    <t>Gail</t>
-  </si>
-  <si>
-    <t>L'esperance</t>
-  </si>
-  <si>
-    <t>yogabygail@gmail.com</t>
-  </si>
-  <si>
-    <t>CA</t>
-  </si>
-  <si>
-    <t>Rebecca</t>
-  </si>
-  <si>
-    <t>Hatman</t>
-  </si>
-  <si>
-    <t>rebecca.hatman@gmail.com</t>
-  </si>
-  <si>
-    <t>San Diego, CA</t>
-  </si>
-  <si>
-    <t>Melody</t>
-  </si>
-  <si>
-    <t>Friedman</t>
-  </si>
-  <si>
-    <t>760-212-1481</t>
-  </si>
-  <si>
-    <t>melodyfriedman1122@gmail.com</t>
-  </si>
-  <si>
-    <t>Teresa</t>
-  </si>
-  <si>
-    <t>Roberts</t>
-  </si>
-  <si>
-    <t>951-235-9263</t>
-  </si>
-  <si>
-    <t>dtroberts@roadrunner.com</t>
-  </si>
-  <si>
-    <t>Temecula, CA</t>
-  </si>
-  <si>
-    <t>Erika</t>
-  </si>
-  <si>
-    <t>Hallquist</t>
-  </si>
-  <si>
-    <t>760-212-8688</t>
-  </si>
-  <si>
-    <t>era.hallquist@gmail.com</t>
-  </si>
-  <si>
     <t>AL</t>
   </si>
   <si>
@@ -319,24 +159,6 @@
     <t>256-617-2132</t>
   </si>
   <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>Rose</t>
-  </si>
-  <si>
-    <t>Caen</t>
-  </si>
-  <si>
-    <t>561-408-3350</t>
-  </si>
-  <si>
-    <t>yogamedrose@gmail.com</t>
-  </si>
-  <si>
-    <t>Sierra Vista, AZ</t>
-  </si>
-  <si>
     <t>DE</t>
   </si>
   <si>
@@ -367,18 +189,6 @@
     <t>heather.murphy@bethanybeachfire.com</t>
   </si>
   <si>
-    <t>NC</t>
-  </si>
-  <si>
-    <t>Sheena</t>
-  </si>
-  <si>
-    <t>Szuri</t>
-  </si>
-  <si>
-    <t>sheenaps@icloud.com</t>
-  </si>
-  <si>
     <t>PA</t>
   </si>
   <si>
@@ -469,45 +279,12 @@
     <t>Miami and Doral, FL</t>
   </si>
   <si>
-    <t>Jupiter, FL</t>
-  </si>
-  <si>
-    <t>New Bern, NC</t>
-  </si>
-  <si>
-    <t>Pompano VA and Boca Raton HQ</t>
-  </si>
-  <si>
-    <t>Boca Raton HQ</t>
-  </si>
-  <si>
     <t xml:space="preserve">SouthCOM </t>
   </si>
   <si>
-    <t>Oceanview Methodist Church</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private Class-Port St. Lucie </t>
-  </si>
-  <si>
-    <t>Ardie Copas Veterans Nursing Home</t>
-  </si>
-  <si>
     <t>Send email inquiry</t>
   </si>
   <si>
-    <t xml:space="preserve">Ft. Huachuca
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Warrior Healing Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roses Poses
-</t>
-  </si>
-  <si>
     <t>Ocean Vayu</t>
   </si>
   <si>
@@ -524,6 +301,21 @@
   </si>
   <si>
     <t>New York, NY</t>
+  </si>
+  <si>
+    <t>ptejas@gmail.com</t>
+  </si>
+  <si>
+    <t>cdrbingo@gmail.com</t>
+  </si>
+  <si>
+    <t>Pompano Vet Center</t>
+  </si>
+  <si>
+    <t>Pompano Beach, FL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boca Raton HQ </t>
   </si>
 </sst>
 </file>
@@ -535,7 +327,7 @@
     <numFmt numFmtId="165" formatCode="dddd"/>
     <numFmt numFmtId="166" formatCode="h&quot;:&quot;mm&quot; &quot;AM/PM"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -643,6 +435,12 @@
       <color rgb="FF434343"/>
       <name val="Raleway"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -697,8 +495,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -745,9 +544,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -813,123 +609,31 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Raleway"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF93C47D"/>
-          <bgColor rgb="FF93C47D"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Raleway"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF93C47D"/>
-          <bgColor rgb="FF93C47D"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Raleway"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF93C47D"/>
-          <bgColor rgb="FF93C47D"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Raleway"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF93C47D"/>
-          <bgColor rgb="FF93C47D"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <font>
         <b val="0"/>
@@ -1069,32 +773,32 @@
   </dxfs>
   <tableStyles count="7">
     <tableStyle name="Roster-style" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="firstRowStripe" dxfId="18"/>
-      <tableStyleElement type="secondRowStripe" dxfId="17"/>
-    </tableStyle>
-    <tableStyle name="Roster-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="secondRowStripe" dxfId="15"/>
-    </tableStyle>
-    <tableStyle name="Roster-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
       <tableStyleElement type="secondRowStripe" dxfId="13"/>
     </tableStyle>
-    <tableStyle name="Roster-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
+    <tableStyle name="Roster-style 2" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="firstRowStripe" dxfId="12"/>
       <tableStyleElement type="secondRowStripe" dxfId="11"/>
     </tableStyle>
-    <tableStyle name="Roster-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
+    <tableStyle name="Roster-style 3" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
       <tableStyleElement type="firstRowStripe" dxfId="10"/>
       <tableStyleElement type="secondRowStripe" dxfId="9"/>
     </tableStyle>
-    <tableStyle name="Roster-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
+    <tableStyle name="Roster-style 4" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="secondRowStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Schedule-style" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
+    <tableStyle name="Roster-style 5" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
       <tableStyleElement type="firstRowStripe" dxfId="6"/>
       <tableStyleElement type="secondRowStripe" dxfId="5"/>
+    </tableStyle>
+    <tableStyle name="Roster-style 6" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="4"/>
+      <tableStyleElement type="secondRowStripe" dxfId="3"/>
+    </tableStyle>
+    <tableStyle name="Schedule-style" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1109,7 +813,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="B4:I29" headerRowCount="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="B4:I23" headerRowCount="0">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2"/>
@@ -1125,45 +829,13 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="B31:I34" headerRowCount="0">
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Column4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Column5" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Column6"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Column7"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Column8"/>
-  </tableColumns>
-  <tableStyleInfo name="Roster-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table_3" displayName="Table_3" ref="B40:I40" headerRowCount="0">
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Column4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Column5" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Column6"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Column7"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Column8"/>
-  </tableColumns>
-  <tableStyleInfo name="Roster-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table_4" displayName="Table_4" ref="B53:I53" headerRowCount="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table_4" displayName="Table_4" ref="B35:I35" headerRowCount="0">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Column2"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Column3"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Column4"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Column5" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Column5" dataDxfId="0"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Column6"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Column7"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Column8"/>
@@ -1172,8 +844,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Table_6" displayName="Table_6" ref="B67:I168" headerRowCount="0">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Table_6" displayName="Table_6" ref="B49:I150" headerRowCount="0">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Column1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Column2"/>
@@ -1188,39 +860,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5FE331ED-A8DC-4A80-AD49-2010ACE88DE7}" name="Table_36" displayName="Table_36" ref="B41:I41" headerRowCount="0">
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{065CB549-E4D8-432D-8560-9B73299C8A26}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{7E8620AA-A820-4B0D-AD3B-B2217E1522DB}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{A696797F-E728-4951-A9FA-8EF63512CC98}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{E074CE62-7DA6-4A76-9841-D9658EDB1B3C}" name="Column4"/>
-    <tableColumn id="5" xr3:uid="{13BD735D-060B-4AE4-82A3-7AEE6461D1B2}" name="Column5" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{D2A01804-F44A-4621-A5A5-8ED083C781E2}" name="Column6"/>
-    <tableColumn id="7" xr3:uid="{9E008BA4-03B8-4602-B826-A4A9206CA645}" name="Column7"/>
-    <tableColumn id="8" xr3:uid="{CC489D1A-4BAA-433A-9B25-BDFBA9DC1268}" name="Column8"/>
-  </tableColumns>
-  <tableStyleInfo name="Roster-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{6CA8BFEB-7B37-4A85-AE19-DD67631CDCB7}" name="Table_369" displayName="Table_369" ref="B42:I42" headerRowCount="0">
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{4D5AFB46-DCEB-4E29-B886-C57EE88EC873}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{F9293F27-9667-4B14-8F91-643597A5E63B}" name="Column2"/>
-    <tableColumn id="3" xr3:uid="{166E3622-1F32-4E77-89D8-5186053F0A0F}" name="Column3"/>
-    <tableColumn id="4" xr3:uid="{AACD78EC-6B2B-4504-BFC0-FA780AAC6DC5}" name="Column4"/>
-    <tableColumn id="5" xr3:uid="{F43A4C90-4FC7-4650-AB79-F3F4574D0C27}" name="Column5" dataDxfId="0"/>
-    <tableColumn id="6" xr3:uid="{BD7B4AFF-0B91-4553-A4A6-25343BD44284}" name="Column6"/>
-    <tableColumn id="7" xr3:uid="{BD7842CC-8274-48F9-B706-2673F8240BDA}" name="Column7"/>
-    <tableColumn id="8" xr3:uid="{345D8F19-A4C1-4274-82BE-43E5D8B1B220}" name="Column8"/>
-  </tableColumns>
-  <tableStyleInfo name="Roster-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Table_7" displayName="Table_7" ref="B5:I20" headerRowCount="0">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Column1"/>
@@ -1557,17 +1197,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:J150"/>
+  <sheetFormatPr defaultColWidth="12.6796875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="3" width="13.109375" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" customWidth="1"/>
-    <col min="5" max="5" width="31.6640625" customWidth="1"/>
-    <col min="6" max="6" width="29.21875" customWidth="1"/>
-    <col min="7" max="7" width="40.6640625" customWidth="1"/>
-    <col min="8" max="9" width="26.109375" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.08984375" customWidth="1"/>
+    <col min="2" max="3" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="14.08984375" customWidth="1"/>
+    <col min="5" max="5" width="31.6796875" customWidth="1"/>
+    <col min="6" max="6" width="29.2265625" customWidth="1"/>
+    <col min="7" max="7" width="40.6796875" customWidth="1"/>
+    <col min="8" max="9" width="26.08984375" customWidth="1"/>
+    <col min="10" max="10" width="16.6796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="12" customHeight="1">
@@ -1584,14 +1224,14 @@
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1">
       <c r="A2" s="4"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
       <c r="J2" s="4"/>
     </row>
     <row r="3" spans="1:10" ht="24" customHeight="1">
@@ -1609,7 +1249,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>160</v>
+        <v>87</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>4</v>
@@ -1637,10 +1277,10 @@
         <v>10</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>11</v>
@@ -1653,23 +1293,25 @@
     <row r="5" spans="1:10" ht="21" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" s="9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="10"/>
+        <v>19</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="E5" s="10" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I5" s="11" t="s">
         <v>12</v>
@@ -1679,25 +1321,25 @@
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="8"/>
       <c r="B6" s="9" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>158</v>
+        <v>85</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>12</v>
@@ -1706,114 +1348,116 @@
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="8"/>
-      <c r="B7" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>24</v>
-      </c>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
       <c r="D7" s="10"/>
-      <c r="E7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>12</v>
-      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
       <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
+      <c r="B8" s="13"/>
       <c r="C8" s="9"/>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="8"/>
     </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="8"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" ht="24" customHeight="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="7" t="s">
+    <row r="9" spans="1:10" ht="24" customHeight="1">
+      <c r="A9" s="6"/>
+      <c r="B9" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C9" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E9" s="7" t="s">
         <v>3</v>
       </c>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10" ht="22.5" customHeight="1">
+      <c r="A10" s="8"/>
+      <c r="B10" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="J10" s="6"/>
-    </row>
-    <row r="11" spans="1:10" ht="22.5" customHeight="1">
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10" ht="18.75" customHeight="1">
       <c r="A11" s="8"/>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
+      <c r="D11" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>12</v>
+      </c>
       <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:10" ht="18.75" customHeight="1">
       <c r="A12" s="8"/>
       <c r="B12" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>30</v>
+      <c r="E12" s="51" t="s">
+        <v>90</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>142</v>
+        <v>79</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>12</v>
@@ -1823,23 +1467,25 @@
     <row r="13" spans="1:10" ht="18.75" customHeight="1">
       <c r="A13" s="8"/>
       <c r="B13" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>33</v>
-      </c>
       <c r="F13" s="15" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>147</v>
+        <v>81</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>12</v>
@@ -1848,1027 +1494,773 @@
     </row>
     <row r="14" spans="1:10" ht="18.75" customHeight="1">
       <c r="A14" s="8"/>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="E14" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="F14" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="H14" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="J14" s="8"/>
+      <c r="J14" s="18"/>
     </row>
     <row r="15" spans="1:10" ht="18.75" customHeight="1">
       <c r="A15" s="8"/>
-      <c r="B15" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>12</v>
-      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
       <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:10" ht="18.75" customHeight="1">
       <c r="A16" s="8"/>
-      <c r="B16" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>12</v>
-      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
       <c r="J16" s="8"/>
     </row>
     <row r="17" spans="1:10" ht="18.75" customHeight="1">
       <c r="A17" s="8"/>
-      <c r="B17" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="16" t="s">
-        <v>12</v>
-      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
       <c r="J17" s="8"/>
     </row>
     <row r="18" spans="1:10" ht="18.75" customHeight="1">
       <c r="A18" s="8"/>
-      <c r="B18" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="I18" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J18" s="19"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10" ht="18.75" customHeight="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G19" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="18"/>
     </row>
     <row r="20" spans="1:10" ht="18.75" customHeight="1">
       <c r="A20" s="8"/>
-      <c r="B20" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="18"/>
     </row>
     <row r="21" spans="1:10" ht="18.75" customHeight="1">
       <c r="A21" s="8"/>
-      <c r="B21" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D21" s="18"/>
-      <c r="E21" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="24"/>
     </row>
     <row r="22" spans="1:10" ht="18.75" customHeight="1">
       <c r="A22" s="8"/>
-      <c r="B22" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" s="18"/>
-      <c r="E22" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="18"/>
     </row>
     <row r="23" spans="1:10" ht="18.75" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
       <c r="F23" s="15"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="8"/>
-    </row>
-    <row r="24" spans="1:10" ht="18.75" customHeight="1">
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="1:10" ht="31.5" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
       <c r="J24" s="8"/>
     </row>
-    <row r="25" spans="1:10" ht="18.75" customHeight="1">
+    <row r="25" spans="1:10" ht="16.5" customHeight="1">
       <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
+      <c r="B25" s="21" t="s">
+        <v>37</v>
+      </c>
       <c r="C25" s="8"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="19"/>
-    </row>
-    <row r="26" spans="1:10" ht="18.75" customHeight="1">
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" spans="1:10" ht="16.5" customHeight="1">
       <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="19"/>
-    </row>
-    <row r="27" spans="1:10" ht="18.75" customHeight="1">
+      <c r="B26" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="F26" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" ht="16.5" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="25"/>
-    </row>
-    <row r="28" spans="1:10" ht="18.75" customHeight="1">
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="8"/>
+    </row>
+    <row r="28" spans="1:10" ht="16.5" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="19"/>
-    </row>
-    <row r="29" spans="1:10" ht="18.75" customHeight="1">
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="8"/>
+    </row>
+    <row r="29" spans="1:10" ht="16.5" customHeight="1">
       <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
+      <c r="B29" s="21" t="s">
+        <v>41</v>
+      </c>
       <c r="C29" s="8"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="19"/>
-    </row>
-    <row r="30" spans="1:10" ht="18.75" customHeight="1">
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="8"/>
+    </row>
+    <row r="30" spans="1:10" ht="16.5" customHeight="1">
       <c r="A30" s="8"/>
-      <c r="B30" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
+      <c r="B30" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G30" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="H30" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I30" s="23" t="s">
+        <v>12</v>
+      </c>
       <c r="J30" s="8"/>
     </row>
-    <row r="31" spans="1:10" ht="18.75" customHeight="1">
+    <row r="31" spans="1:10" ht="21" customHeight="1">
       <c r="A31" s="8"/>
-      <c r="B31" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>74</v>
-      </c>
-      <c r="D31" s="23"/>
-      <c r="E31" s="16" t="s">
-        <v>75</v>
+      <c r="B31" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>50</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G31" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="H31" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I31" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G31" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="I31" s="23" t="s">
         <v>12</v>
       </c>
       <c r="J31" s="8"/>
     </row>
-    <row r="32" spans="1:10" ht="18.75" customHeight="1">
+    <row r="32" spans="1:10" ht="16.5" customHeight="1">
       <c r="A32" s="8"/>
-      <c r="B32" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="16" t="s">
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="8"/>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="8"/>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A34" s="8"/>
+      <c r="B34" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="8"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A35" s="8"/>
+      <c r="B35" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="D32" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="H32" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I32" s="16" t="s">
+      <c r="G35" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="J32" s="25"/>
-    </row>
-    <row r="33" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A33" s="8"/>
-      <c r="B33" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="E33" s="15" t="s">
+      <c r="J35" s="8"/>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="8"/>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A37" s="8"/>
+      <c r="B37" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37" s="8"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="8"/>
+    </row>
+    <row r="38" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A38" s="8"/>
+      <c r="B38" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F38" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="J38" s="8"/>
+    </row>
+    <row r="39" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="8"/>
+    </row>
+    <row r="40" spans="1:10" ht="27.65" customHeight="1">
+      <c r="A40" s="4"/>
+      <c r="B40" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" spans="1:10" ht="30" customHeight="1">
+      <c r="A41" s="4"/>
+      <c r="B41" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G41" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="F33" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G33" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="I33" s="15" t="s">
+      <c r="H41" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="I41" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="J33" s="8"/>
-    </row>
-    <row r="34" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A34" s="8"/>
-      <c r="B34" s="16" t="s">
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" spans="1:10" ht="24" customHeight="1">
+      <c r="A42" s="6"/>
+      <c r="B42" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="8"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="6"/>
+    </row>
+    <row r="43" spans="1:10" ht="21" customHeight="1">
+      <c r="A43" s="8"/>
+      <c r="B43" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="I43" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="C34" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G34" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="H34" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I34" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="J34" s="8"/>
-    </row>
-    <row r="35" spans="1:10" ht="31.5" customHeight="1">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="8"/>
-    </row>
-    <row r="36" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A36" s="8"/>
-      <c r="B36" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="8"/>
-    </row>
-    <row r="37" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A37" s="8"/>
-      <c r="B37" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="D37" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="E37" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="G37" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="H37" s="51" t="s">
-        <v>25</v>
-      </c>
-      <c r="I37" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="J37" s="8"/>
-    </row>
-    <row r="38" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
-      <c r="G38" s="21"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="21"/>
-      <c r="J38" s="8"/>
-    </row>
-    <row r="39" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A39" s="8"/>
-      <c r="B39" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="C39" s="8"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
-      <c r="G39" s="21"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="21"/>
-      <c r="J39" s="8"/>
-    </row>
-    <row r="40" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A40" s="8"/>
-      <c r="B40" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E40" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G40" s="50" t="s">
-        <v>153</v>
-      </c>
-      <c r="H40" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="I40" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="J40" s="8"/>
-    </row>
-    <row r="41" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A41" s="8"/>
-      <c r="B41" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E41" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G41" s="50" t="s">
-        <v>154</v>
-      </c>
-      <c r="H41" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="I41" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="J41" s="8"/>
-    </row>
-    <row r="42" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A42" s="8"/>
-      <c r="B42" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="E42" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G42" s="50" t="s">
-        <v>155</v>
-      </c>
-      <c r="H42" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="I42" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="J42" s="8"/>
-    </row>
-    <row r="43" spans="1:10" ht="16.5" customHeight="1">
-      <c r="A43" s="8"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="15"/>
       <c r="J43" s="8"/>
     </row>
-    <row r="44" spans="1:10" ht="16.5" customHeight="1">
+    <row r="44" spans="1:10" ht="19.5" customHeight="1">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
-      <c r="D44" s="21"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="21"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
       <c r="J44" s="8"/>
     </row>
-    <row r="45" spans="1:10" ht="16.5" customHeight="1">
+    <row r="45" spans="1:10" ht="19.5" customHeight="1">
       <c r="A45" s="8"/>
-      <c r="B45" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="8"/>
-      <c r="D45" s="21"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="21"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
       <c r="J45" s="8"/>
     </row>
-    <row r="46" spans="1:10" ht="16.5" customHeight="1">
+    <row r="46" spans="1:10" ht="19.5" customHeight="1">
       <c r="A46" s="8"/>
-      <c r="B46" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="C46" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="D46" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E46" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G46" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="H46" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="I46" s="24" t="s">
-        <v>12</v>
-      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
       <c r="J46" s="8"/>
     </row>
-    <row r="47" spans="1:10" ht="21" customHeight="1">
+    <row r="47" spans="1:10" ht="19.5" customHeight="1">
       <c r="A47" s="8"/>
-      <c r="B47" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D47" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="E47" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="F47" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G47" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="H47" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="I47" s="24" t="s">
-        <v>12</v>
-      </c>
+      <c r="B47" s="46"/>
+      <c r="C47" s="47"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
+      <c r="G47" s="47"/>
+      <c r="H47" s="47"/>
+      <c r="I47" s="47"/>
       <c r="J47" s="8"/>
     </row>
-    <row r="48" spans="1:10" ht="16.5" customHeight="1">
+    <row r="48" spans="1:10" ht="19.5" customHeight="1">
       <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
-      <c r="G48" s="21"/>
-      <c r="H48" s="21"/>
-      <c r="I48" s="21"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
+      <c r="H48" s="7"/>
+      <c r="I48" s="7"/>
       <c r="J48" s="8"/>
     </row>
-    <row r="49" spans="1:10" ht="16.5" customHeight="1">
+    <row r="49" spans="1:10" ht="19.5" customHeight="1">
       <c r="A49" s="8"/>
-      <c r="B49" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="C49" s="8"/>
-      <c r="D49" s="21"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
-      <c r="G49" s="21"/>
-      <c r="H49" s="21"/>
-      <c r="I49" s="21"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
       <c r="J49" s="8"/>
     </row>
-    <row r="50" spans="1:10" ht="15.75" customHeight="1">
+    <row r="50" spans="1:10" ht="19.5" customHeight="1">
       <c r="A50" s="8"/>
-      <c r="B50" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C50" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="D50" s="23"/>
-      <c r="E50" s="23" t="s">
-        <v>113</v>
-      </c>
-      <c r="F50" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G50" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="H50" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="I50" s="23" t="s">
-        <v>12</v>
-      </c>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
       <c r="J50" s="8"/>
     </row>
-    <row r="51" spans="1:10" ht="15.75" customHeight="1">
+    <row r="51" spans="1:10" ht="19.5" customHeight="1">
       <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="21"/>
-      <c r="H51" s="21"/>
-      <c r="I51" s="21"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
       <c r="J51" s="8"/>
     </row>
-    <row r="52" spans="1:10" ht="15.75" customHeight="1">
+    <row r="52" spans="1:10" ht="19.5" customHeight="1">
       <c r="A52" s="8"/>
-      <c r="B52" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="C52" s="8"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="21"/>
-      <c r="G52" s="21"/>
-      <c r="H52" s="21"/>
-      <c r="I52" s="21"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
       <c r="J52" s="8"/>
     </row>
-    <row r="53" spans="1:10" ht="15.75" customHeight="1">
+    <row r="53" spans="1:10" ht="19.5" customHeight="1">
       <c r="A53" s="8"/>
-      <c r="B53" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D53" s="27"/>
-      <c r="E53" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G53" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="H53" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="I53" s="28" t="s">
-        <v>12</v>
-      </c>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
       <c r="J53" s="8"/>
     </row>
-    <row r="54" spans="1:10" ht="15.75" customHeight="1">
+    <row r="54" spans="1:10" ht="19.5" customHeight="1">
       <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="21"/>
-      <c r="G54" s="21"/>
-      <c r="H54" s="21"/>
-      <c r="I54" s="21"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
       <c r="J54" s="8"/>
     </row>
-    <row r="55" spans="1:10" ht="15.75" customHeight="1">
+    <row r="55" spans="1:10" ht="19.5" customHeight="1">
       <c r="A55" s="8"/>
-      <c r="B55" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C55" s="8"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
       <c r="J55" s="8"/>
     </row>
-    <row r="56" spans="1:10" ht="15.75" customHeight="1">
+    <row r="56" spans="1:10" ht="19.5" customHeight="1">
       <c r="A56" s="8"/>
-      <c r="B56" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="F56" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G56" s="23"/>
-      <c r="H56" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="I56" s="23" t="s">
-        <v>159</v>
-      </c>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11"/>
       <c r="J56" s="8"/>
     </row>
-    <row r="57" spans="1:10" ht="15.75" customHeight="1">
+    <row r="57" spans="1:10" ht="19.5" customHeight="1">
       <c r="A57" s="8"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="21"/>
-      <c r="G57" s="21"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="21"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="28"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
       <c r="J57" s="8"/>
     </row>
-    <row r="58" spans="1:10" ht="27.6" customHeight="1">
-      <c r="A58" s="4"/>
-      <c r="B58" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="C58" s="8"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
-      <c r="J58" s="4"/>
-    </row>
-    <row r="59" spans="1:10" ht="30" customHeight="1">
-      <c r="A59" s="4"/>
-      <c r="B59" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="C59" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="F59" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G59" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="H59" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="I59" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="J59" s="4"/>
-    </row>
-    <row r="60" spans="1:10" ht="24" customHeight="1">
-      <c r="A60" s="6"/>
-      <c r="B60" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="C60" s="8"/>
-      <c r="D60" s="21"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="21"/>
-      <c r="G60" s="21"/>
-      <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="6"/>
-    </row>
-    <row r="61" spans="1:10" ht="21" customHeight="1">
+    <row r="58" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A58" s="8"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="8"/>
+    </row>
+    <row r="59" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A59" s="8"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="28"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="8"/>
+    </row>
+    <row r="60" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A60" s="8"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="8"/>
+    </row>
+    <row r="61" spans="1:10" ht="19.5" customHeight="1">
       <c r="A61" s="8"/>
-      <c r="B61" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="C61" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="F61" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G61" s="23"/>
-      <c r="H61" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="I61" s="23" t="s">
-        <v>159</v>
-      </c>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="10"/>
+      <c r="G61" s="10"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
       <c r="J61" s="8"/>
     </row>
     <row r="62" spans="1:10" ht="19.5" customHeight="1">
       <c r="A62" s="8"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="28"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="10"/>
+      <c r="G62" s="10"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11"/>
       <c r="J62" s="8"/>
     </row>
     <row r="63" spans="1:10" ht="19.5" customHeight="1">
       <c r="A63" s="8"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="5"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="28"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="10"/>
+      <c r="G63" s="10"/>
+      <c r="H63" s="11"/>
+      <c r="I63" s="11"/>
       <c r="J63" s="8"/>
     </row>
     <row r="64" spans="1:10" ht="19.5" customHeight="1">
       <c r="A64" s="8"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="10"/>
+      <c r="G64" s="10"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="11"/>
       <c r="J64" s="8"/>
     </row>
     <row r="65" spans="1:10" ht="19.5" customHeight="1">
       <c r="A65" s="8"/>
-      <c r="B65" s="47"/>
-      <c r="C65" s="46"/>
-      <c r="D65" s="46"/>
-      <c r="E65" s="46"/>
-      <c r="F65" s="46"/>
-      <c r="G65" s="46"/>
-      <c r="H65" s="46"/>
-      <c r="I65" s="46"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="10"/>
+      <c r="G65" s="10"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
       <c r="J65" s="8"/>
     </row>
     <row r="66" spans="1:10" ht="19.5" customHeight="1">
       <c r="A66" s="8"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="7"/>
-      <c r="H66" s="7"/>
-      <c r="I66" s="7"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="28"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="10"/>
+      <c r="G66" s="10"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
       <c r="J66" s="8"/>
     </row>
     <row r="67" spans="1:10" ht="19.5" customHeight="1">
       <c r="A67" s="8"/>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
-      <c r="D67" s="10"/>
+      <c r="D67" s="28"/>
       <c r="E67" s="10"/>
       <c r="F67" s="10"/>
       <c r="G67" s="10"/>
@@ -2880,7 +2272,7 @@
       <c r="A68" s="8"/>
       <c r="B68" s="9"/>
       <c r="C68" s="9"/>
-      <c r="D68" s="10"/>
+      <c r="D68" s="28"/>
       <c r="E68" s="10"/>
       <c r="F68" s="10"/>
       <c r="G68" s="10"/>
@@ -2892,7 +2284,7 @@
       <c r="A69" s="8"/>
       <c r="B69" s="9"/>
       <c r="C69" s="9"/>
-      <c r="D69" s="10"/>
+      <c r="D69" s="28"/>
       <c r="E69" s="10"/>
       <c r="F69" s="10"/>
       <c r="G69" s="10"/>
@@ -2904,7 +2296,7 @@
       <c r="A70" s="8"/>
       <c r="B70" s="9"/>
       <c r="C70" s="9"/>
-      <c r="D70" s="29"/>
+      <c r="D70" s="28"/>
       <c r="E70" s="10"/>
       <c r="F70" s="10"/>
       <c r="G70" s="10"/>
@@ -2916,7 +2308,7 @@
       <c r="A71" s="8"/>
       <c r="B71" s="9"/>
       <c r="C71" s="9"/>
-      <c r="D71" s="29"/>
+      <c r="D71" s="28"/>
       <c r="E71" s="10"/>
       <c r="F71" s="10"/>
       <c r="G71" s="10"/>
@@ -2928,7 +2320,7 @@
       <c r="A72" s="8"/>
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
-      <c r="D72" s="29"/>
+      <c r="D72" s="28"/>
       <c r="E72" s="10"/>
       <c r="F72" s="10"/>
       <c r="G72" s="10"/>
@@ -2940,7 +2332,7 @@
       <c r="A73" s="8"/>
       <c r="B73" s="9"/>
       <c r="C73" s="9"/>
-      <c r="D73" s="29"/>
+      <c r="D73" s="28"/>
       <c r="E73" s="10"/>
       <c r="F73" s="10"/>
       <c r="G73" s="10"/>
@@ -2952,7 +2344,7 @@
       <c r="A74" s="8"/>
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
-      <c r="D74" s="29"/>
+      <c r="D74" s="28"/>
       <c r="E74" s="10"/>
       <c r="F74" s="10"/>
       <c r="G74" s="10"/>
@@ -2964,7 +2356,7 @@
       <c r="A75" s="8"/>
       <c r="B75" s="9"/>
       <c r="C75" s="9"/>
-      <c r="D75" s="29"/>
+      <c r="D75" s="28"/>
       <c r="E75" s="10"/>
       <c r="F75" s="10"/>
       <c r="G75" s="10"/>
@@ -2976,7 +2368,7 @@
       <c r="A76" s="8"/>
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
-      <c r="D76" s="29"/>
+      <c r="D76" s="28"/>
       <c r="E76" s="10"/>
       <c r="F76" s="10"/>
       <c r="G76" s="10"/>
@@ -2988,7 +2380,7 @@
       <c r="A77" s="8"/>
       <c r="B77" s="9"/>
       <c r="C77" s="9"/>
-      <c r="D77" s="29"/>
+      <c r="D77" s="28"/>
       <c r="E77" s="10"/>
       <c r="F77" s="10"/>
       <c r="G77" s="10"/>
@@ -3000,7 +2392,7 @@
       <c r="A78" s="8"/>
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
-      <c r="D78" s="29"/>
+      <c r="D78" s="28"/>
       <c r="E78" s="10"/>
       <c r="F78" s="10"/>
       <c r="G78" s="10"/>
@@ -3012,7 +2404,7 @@
       <c r="A79" s="8"/>
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
-      <c r="D79" s="29"/>
+      <c r="D79" s="28"/>
       <c r="E79" s="10"/>
       <c r="F79" s="10"/>
       <c r="G79" s="10"/>
@@ -3024,7 +2416,7 @@
       <c r="A80" s="8"/>
       <c r="B80" s="9"/>
       <c r="C80" s="9"/>
-      <c r="D80" s="29"/>
+      <c r="D80" s="28"/>
       <c r="E80" s="10"/>
       <c r="F80" s="10"/>
       <c r="G80" s="10"/>
@@ -3036,7 +2428,7 @@
       <c r="A81" s="8"/>
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
-      <c r="D81" s="29"/>
+      <c r="D81" s="28"/>
       <c r="E81" s="10"/>
       <c r="F81" s="10"/>
       <c r="G81" s="10"/>
@@ -3048,7 +2440,7 @@
       <c r="A82" s="8"/>
       <c r="B82" s="9"/>
       <c r="C82" s="9"/>
-      <c r="D82" s="29"/>
+      <c r="D82" s="28"/>
       <c r="E82" s="10"/>
       <c r="F82" s="10"/>
       <c r="G82" s="10"/>
@@ -3060,7 +2452,7 @@
       <c r="A83" s="8"/>
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
-      <c r="D83" s="29"/>
+      <c r="D83" s="28"/>
       <c r="E83" s="10"/>
       <c r="F83" s="10"/>
       <c r="G83" s="10"/>
@@ -3072,7 +2464,7 @@
       <c r="A84" s="8"/>
       <c r="B84" s="9"/>
       <c r="C84" s="9"/>
-      <c r="D84" s="29"/>
+      <c r="D84" s="28"/>
       <c r="E84" s="10"/>
       <c r="F84" s="10"/>
       <c r="G84" s="10"/>
@@ -3084,7 +2476,7 @@
       <c r="A85" s="8"/>
       <c r="B85" s="9"/>
       <c r="C85" s="9"/>
-      <c r="D85" s="29"/>
+      <c r="D85" s="28"/>
       <c r="E85" s="10"/>
       <c r="F85" s="10"/>
       <c r="G85" s="10"/>
@@ -3096,7 +2488,7 @@
       <c r="A86" s="8"/>
       <c r="B86" s="9"/>
       <c r="C86" s="9"/>
-      <c r="D86" s="29"/>
+      <c r="D86" s="28"/>
       <c r="E86" s="10"/>
       <c r="F86" s="10"/>
       <c r="G86" s="10"/>
@@ -3108,7 +2500,7 @@
       <c r="A87" s="8"/>
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
-      <c r="D87" s="29"/>
+      <c r="D87" s="28"/>
       <c r="E87" s="10"/>
       <c r="F87" s="10"/>
       <c r="G87" s="10"/>
@@ -3120,7 +2512,7 @@
       <c r="A88" s="8"/>
       <c r="B88" s="9"/>
       <c r="C88" s="9"/>
-      <c r="D88" s="29"/>
+      <c r="D88" s="28"/>
       <c r="E88" s="10"/>
       <c r="F88" s="10"/>
       <c r="G88" s="10"/>
@@ -3132,7 +2524,7 @@
       <c r="A89" s="8"/>
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
-      <c r="D89" s="29"/>
+      <c r="D89" s="28"/>
       <c r="E89" s="10"/>
       <c r="F89" s="10"/>
       <c r="G89" s="10"/>
@@ -3144,7 +2536,7 @@
       <c r="A90" s="8"/>
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
-      <c r="D90" s="29"/>
+      <c r="D90" s="28"/>
       <c r="E90" s="10"/>
       <c r="F90" s="10"/>
       <c r="G90" s="10"/>
@@ -3156,7 +2548,7 @@
       <c r="A91" s="8"/>
       <c r="B91" s="9"/>
       <c r="C91" s="9"/>
-      <c r="D91" s="29"/>
+      <c r="D91" s="28"/>
       <c r="E91" s="10"/>
       <c r="F91" s="10"/>
       <c r="G91" s="10"/>
@@ -3168,7 +2560,7 @@
       <c r="A92" s="8"/>
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
-      <c r="D92" s="29"/>
+      <c r="D92" s="28"/>
       <c r="E92" s="10"/>
       <c r="F92" s="10"/>
       <c r="G92" s="10"/>
@@ -3180,7 +2572,7 @@
       <c r="A93" s="8"/>
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
-      <c r="D93" s="29"/>
+      <c r="D93" s="28"/>
       <c r="E93" s="10"/>
       <c r="F93" s="10"/>
       <c r="G93" s="10"/>
@@ -3192,7 +2584,7 @@
       <c r="A94" s="8"/>
       <c r="B94" s="9"/>
       <c r="C94" s="9"/>
-      <c r="D94" s="29"/>
+      <c r="D94" s="28"/>
       <c r="E94" s="10"/>
       <c r="F94" s="10"/>
       <c r="G94" s="10"/>
@@ -3204,7 +2596,7 @@
       <c r="A95" s="8"/>
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
-      <c r="D95" s="29"/>
+      <c r="D95" s="28"/>
       <c r="E95" s="10"/>
       <c r="F95" s="10"/>
       <c r="G95" s="10"/>
@@ -3216,7 +2608,7 @@
       <c r="A96" s="8"/>
       <c r="B96" s="9"/>
       <c r="C96" s="9"/>
-      <c r="D96" s="29"/>
+      <c r="D96" s="28"/>
       <c r="E96" s="10"/>
       <c r="F96" s="10"/>
       <c r="G96" s="10"/>
@@ -3228,7 +2620,7 @@
       <c r="A97" s="8"/>
       <c r="B97" s="9"/>
       <c r="C97" s="9"/>
-      <c r="D97" s="29"/>
+      <c r="D97" s="28"/>
       <c r="E97" s="10"/>
       <c r="F97" s="10"/>
       <c r="G97" s="10"/>
@@ -3240,7 +2632,7 @@
       <c r="A98" s="8"/>
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
-      <c r="D98" s="29"/>
+      <c r="D98" s="28"/>
       <c r="E98" s="10"/>
       <c r="F98" s="10"/>
       <c r="G98" s="10"/>
@@ -3252,7 +2644,7 @@
       <c r="A99" s="8"/>
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
-      <c r="D99" s="29"/>
+      <c r="D99" s="28"/>
       <c r="E99" s="10"/>
       <c r="F99" s="10"/>
       <c r="G99" s="10"/>
@@ -3264,7 +2656,7 @@
       <c r="A100" s="8"/>
       <c r="B100" s="9"/>
       <c r="C100" s="9"/>
-      <c r="D100" s="29"/>
+      <c r="D100" s="28"/>
       <c r="E100" s="10"/>
       <c r="F100" s="10"/>
       <c r="G100" s="10"/>
@@ -3276,7 +2668,7 @@
       <c r="A101" s="8"/>
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
-      <c r="D101" s="29"/>
+      <c r="D101" s="28"/>
       <c r="E101" s="10"/>
       <c r="F101" s="10"/>
       <c r="G101" s="10"/>
@@ -3288,7 +2680,7 @@
       <c r="A102" s="8"/>
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
-      <c r="D102" s="29"/>
+      <c r="D102" s="28"/>
       <c r="E102" s="10"/>
       <c r="F102" s="10"/>
       <c r="G102" s="10"/>
@@ -3300,7 +2692,7 @@
       <c r="A103" s="8"/>
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
-      <c r="D103" s="29"/>
+      <c r="D103" s="28"/>
       <c r="E103" s="10"/>
       <c r="F103" s="10"/>
       <c r="G103" s="10"/>
@@ -3312,7 +2704,7 @@
       <c r="A104" s="8"/>
       <c r="B104" s="9"/>
       <c r="C104" s="9"/>
-      <c r="D104" s="29"/>
+      <c r="D104" s="28"/>
       <c r="E104" s="10"/>
       <c r="F104" s="10"/>
       <c r="G104" s="10"/>
@@ -3324,7 +2716,7 @@
       <c r="A105" s="8"/>
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
-      <c r="D105" s="29"/>
+      <c r="D105" s="28"/>
       <c r="E105" s="10"/>
       <c r="F105" s="10"/>
       <c r="G105" s="10"/>
@@ -3336,7 +2728,7 @@
       <c r="A106" s="8"/>
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
-      <c r="D106" s="29"/>
+      <c r="D106" s="28"/>
       <c r="E106" s="10"/>
       <c r="F106" s="10"/>
       <c r="G106" s="10"/>
@@ -3348,7 +2740,7 @@
       <c r="A107" s="8"/>
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
-      <c r="D107" s="29"/>
+      <c r="D107" s="28"/>
       <c r="E107" s="10"/>
       <c r="F107" s="10"/>
       <c r="G107" s="10"/>
@@ -3360,7 +2752,7 @@
       <c r="A108" s="8"/>
       <c r="B108" s="9"/>
       <c r="C108" s="9"/>
-      <c r="D108" s="29"/>
+      <c r="D108" s="28"/>
       <c r="E108" s="10"/>
       <c r="F108" s="10"/>
       <c r="G108" s="10"/>
@@ -3372,7 +2764,7 @@
       <c r="A109" s="8"/>
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
-      <c r="D109" s="29"/>
+      <c r="D109" s="28"/>
       <c r="E109" s="10"/>
       <c r="F109" s="10"/>
       <c r="G109" s="10"/>
@@ -3384,7 +2776,7 @@
       <c r="A110" s="8"/>
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
-      <c r="D110" s="29"/>
+      <c r="D110" s="28"/>
       <c r="E110" s="10"/>
       <c r="F110" s="10"/>
       <c r="G110" s="10"/>
@@ -3396,7 +2788,7 @@
       <c r="A111" s="8"/>
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
-      <c r="D111" s="29"/>
+      <c r="D111" s="28"/>
       <c r="E111" s="10"/>
       <c r="F111" s="10"/>
       <c r="G111" s="10"/>
@@ -3408,7 +2800,7 @@
       <c r="A112" s="8"/>
       <c r="B112" s="9"/>
       <c r="C112" s="9"/>
-      <c r="D112" s="29"/>
+      <c r="D112" s="28"/>
       <c r="E112" s="10"/>
       <c r="F112" s="10"/>
       <c r="G112" s="10"/>
@@ -3420,7 +2812,7 @@
       <c r="A113" s="8"/>
       <c r="B113" s="9"/>
       <c r="C113" s="9"/>
-      <c r="D113" s="29"/>
+      <c r="D113" s="28"/>
       <c r="E113" s="10"/>
       <c r="F113" s="10"/>
       <c r="G113" s="10"/>
@@ -3432,7 +2824,7 @@
       <c r="A114" s="8"/>
       <c r="B114" s="9"/>
       <c r="C114" s="9"/>
-      <c r="D114" s="29"/>
+      <c r="D114" s="28"/>
       <c r="E114" s="10"/>
       <c r="F114" s="10"/>
       <c r="G114" s="10"/>
@@ -3444,7 +2836,7 @@
       <c r="A115" s="8"/>
       <c r="B115" s="9"/>
       <c r="C115" s="9"/>
-      <c r="D115" s="29"/>
+      <c r="D115" s="28"/>
       <c r="E115" s="10"/>
       <c r="F115" s="10"/>
       <c r="G115" s="10"/>
@@ -3456,7 +2848,7 @@
       <c r="A116" s="8"/>
       <c r="B116" s="9"/>
       <c r="C116" s="9"/>
-      <c r="D116" s="29"/>
+      <c r="D116" s="28"/>
       <c r="E116" s="10"/>
       <c r="F116" s="10"/>
       <c r="G116" s="10"/>
@@ -3468,7 +2860,7 @@
       <c r="A117" s="8"/>
       <c r="B117" s="9"/>
       <c r="C117" s="9"/>
-      <c r="D117" s="29"/>
+      <c r="D117" s="28"/>
       <c r="E117" s="10"/>
       <c r="F117" s="10"/>
       <c r="G117" s="10"/>
@@ -3480,7 +2872,7 @@
       <c r="A118" s="8"/>
       <c r="B118" s="9"/>
       <c r="C118" s="9"/>
-      <c r="D118" s="29"/>
+      <c r="D118" s="28"/>
       <c r="E118" s="10"/>
       <c r="F118" s="10"/>
       <c r="G118" s="10"/>
@@ -3492,7 +2884,7 @@
       <c r="A119" s="8"/>
       <c r="B119" s="9"/>
       <c r="C119" s="9"/>
-      <c r="D119" s="29"/>
+      <c r="D119" s="28"/>
       <c r="E119" s="10"/>
       <c r="F119" s="10"/>
       <c r="G119" s="10"/>
@@ -3504,7 +2896,7 @@
       <c r="A120" s="8"/>
       <c r="B120" s="9"/>
       <c r="C120" s="9"/>
-      <c r="D120" s="29"/>
+      <c r="D120" s="28"/>
       <c r="E120" s="10"/>
       <c r="F120" s="10"/>
       <c r="G120" s="10"/>
@@ -3516,7 +2908,7 @@
       <c r="A121" s="8"/>
       <c r="B121" s="9"/>
       <c r="C121" s="9"/>
-      <c r="D121" s="29"/>
+      <c r="D121" s="28"/>
       <c r="E121" s="10"/>
       <c r="F121" s="10"/>
       <c r="G121" s="10"/>
@@ -3528,7 +2920,7 @@
       <c r="A122" s="8"/>
       <c r="B122" s="9"/>
       <c r="C122" s="9"/>
-      <c r="D122" s="29"/>
+      <c r="D122" s="28"/>
       <c r="E122" s="10"/>
       <c r="F122" s="10"/>
       <c r="G122" s="10"/>
@@ -3540,7 +2932,7 @@
       <c r="A123" s="8"/>
       <c r="B123" s="9"/>
       <c r="C123" s="9"/>
-      <c r="D123" s="29"/>
+      <c r="D123" s="28"/>
       <c r="E123" s="10"/>
       <c r="F123" s="10"/>
       <c r="G123" s="10"/>
@@ -3552,7 +2944,7 @@
       <c r="A124" s="8"/>
       <c r="B124" s="9"/>
       <c r="C124" s="9"/>
-      <c r="D124" s="29"/>
+      <c r="D124" s="28"/>
       <c r="E124" s="10"/>
       <c r="F124" s="10"/>
       <c r="G124" s="10"/>
@@ -3564,7 +2956,7 @@
       <c r="A125" s="8"/>
       <c r="B125" s="9"/>
       <c r="C125" s="9"/>
-      <c r="D125" s="29"/>
+      <c r="D125" s="28"/>
       <c r="E125" s="10"/>
       <c r="F125" s="10"/>
       <c r="G125" s="10"/>
@@ -3576,7 +2968,7 @@
       <c r="A126" s="8"/>
       <c r="B126" s="9"/>
       <c r="C126" s="9"/>
-      <c r="D126" s="29"/>
+      <c r="D126" s="28"/>
       <c r="E126" s="10"/>
       <c r="F126" s="10"/>
       <c r="G126" s="10"/>
@@ -3588,7 +2980,7 @@
       <c r="A127" s="8"/>
       <c r="B127" s="9"/>
       <c r="C127" s="9"/>
-      <c r="D127" s="29"/>
+      <c r="D127" s="28"/>
       <c r="E127" s="10"/>
       <c r="F127" s="10"/>
       <c r="G127" s="10"/>
@@ -3600,7 +2992,7 @@
       <c r="A128" s="8"/>
       <c r="B128" s="9"/>
       <c r="C128" s="9"/>
-      <c r="D128" s="29"/>
+      <c r="D128" s="28"/>
       <c r="E128" s="10"/>
       <c r="F128" s="10"/>
       <c r="G128" s="10"/>
@@ -3612,7 +3004,7 @@
       <c r="A129" s="8"/>
       <c r="B129" s="9"/>
       <c r="C129" s="9"/>
-      <c r="D129" s="29"/>
+      <c r="D129" s="28"/>
       <c r="E129" s="10"/>
       <c r="F129" s="10"/>
       <c r="G129" s="10"/>
@@ -3624,7 +3016,7 @@
       <c r="A130" s="8"/>
       <c r="B130" s="9"/>
       <c r="C130" s="9"/>
-      <c r="D130" s="29"/>
+      <c r="D130" s="28"/>
       <c r="E130" s="10"/>
       <c r="F130" s="10"/>
       <c r="G130" s="10"/>
@@ -3636,7 +3028,7 @@
       <c r="A131" s="8"/>
       <c r="B131" s="9"/>
       <c r="C131" s="9"/>
-      <c r="D131" s="29"/>
+      <c r="D131" s="28"/>
       <c r="E131" s="10"/>
       <c r="F131" s="10"/>
       <c r="G131" s="10"/>
@@ -3648,7 +3040,7 @@
       <c r="A132" s="8"/>
       <c r="B132" s="9"/>
       <c r="C132" s="9"/>
-      <c r="D132" s="29"/>
+      <c r="D132" s="28"/>
       <c r="E132" s="10"/>
       <c r="F132" s="10"/>
       <c r="G132" s="10"/>
@@ -3660,7 +3052,7 @@
       <c r="A133" s="8"/>
       <c r="B133" s="9"/>
       <c r="C133" s="9"/>
-      <c r="D133" s="29"/>
+      <c r="D133" s="28"/>
       <c r="E133" s="10"/>
       <c r="F133" s="10"/>
       <c r="G133" s="10"/>
@@ -3672,7 +3064,7 @@
       <c r="A134" s="8"/>
       <c r="B134" s="9"/>
       <c r="C134" s="9"/>
-      <c r="D134" s="29"/>
+      <c r="D134" s="28"/>
       <c r="E134" s="10"/>
       <c r="F134" s="10"/>
       <c r="G134" s="10"/>
@@ -3684,7 +3076,7 @@
       <c r="A135" s="8"/>
       <c r="B135" s="9"/>
       <c r="C135" s="9"/>
-      <c r="D135" s="29"/>
+      <c r="D135" s="28"/>
       <c r="E135" s="10"/>
       <c r="F135" s="10"/>
       <c r="G135" s="10"/>
@@ -3696,7 +3088,7 @@
       <c r="A136" s="8"/>
       <c r="B136" s="9"/>
       <c r="C136" s="9"/>
-      <c r="D136" s="29"/>
+      <c r="D136" s="28"/>
       <c r="E136" s="10"/>
       <c r="F136" s="10"/>
       <c r="G136" s="10"/>
@@ -3708,7 +3100,7 @@
       <c r="A137" s="8"/>
       <c r="B137" s="9"/>
       <c r="C137" s="9"/>
-      <c r="D137" s="29"/>
+      <c r="D137" s="28"/>
       <c r="E137" s="10"/>
       <c r="F137" s="10"/>
       <c r="G137" s="10"/>
@@ -3720,7 +3112,7 @@
       <c r="A138" s="8"/>
       <c r="B138" s="9"/>
       <c r="C138" s="9"/>
-      <c r="D138" s="29"/>
+      <c r="D138" s="28"/>
       <c r="E138" s="10"/>
       <c r="F138" s="10"/>
       <c r="G138" s="10"/>
@@ -3732,7 +3124,7 @@
       <c r="A139" s="8"/>
       <c r="B139" s="9"/>
       <c r="C139" s="9"/>
-      <c r="D139" s="29"/>
+      <c r="D139" s="28"/>
       <c r="E139" s="10"/>
       <c r="F139" s="10"/>
       <c r="G139" s="10"/>
@@ -3744,7 +3136,7 @@
       <c r="A140" s="8"/>
       <c r="B140" s="9"/>
       <c r="C140" s="9"/>
-      <c r="D140" s="29"/>
+      <c r="D140" s="28"/>
       <c r="E140" s="10"/>
       <c r="F140" s="10"/>
       <c r="G140" s="10"/>
@@ -3756,7 +3148,7 @@
       <c r="A141" s="8"/>
       <c r="B141" s="9"/>
       <c r="C141" s="9"/>
-      <c r="D141" s="29"/>
+      <c r="D141" s="28"/>
       <c r="E141" s="10"/>
       <c r="F141" s="10"/>
       <c r="G141" s="10"/>
@@ -3768,7 +3160,7 @@
       <c r="A142" s="8"/>
       <c r="B142" s="9"/>
       <c r="C142" s="9"/>
-      <c r="D142" s="29"/>
+      <c r="D142" s="28"/>
       <c r="E142" s="10"/>
       <c r="F142" s="10"/>
       <c r="G142" s="10"/>
@@ -3780,7 +3172,7 @@
       <c r="A143" s="8"/>
       <c r="B143" s="9"/>
       <c r="C143" s="9"/>
-      <c r="D143" s="29"/>
+      <c r="D143" s="28"/>
       <c r="E143" s="10"/>
       <c r="F143" s="10"/>
       <c r="G143" s="10"/>
@@ -3792,7 +3184,7 @@
       <c r="A144" s="8"/>
       <c r="B144" s="9"/>
       <c r="C144" s="9"/>
-      <c r="D144" s="29"/>
+      <c r="D144" s="28"/>
       <c r="E144" s="10"/>
       <c r="F144" s="10"/>
       <c r="G144" s="10"/>
@@ -3800,298 +3192,83 @@
       <c r="I144" s="11"/>
       <c r="J144" s="8"/>
     </row>
-    <row r="145" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A145" s="8"/>
+    <row r="145" spans="2:9" ht="15.75" customHeight="1">
       <c r="B145" s="9"/>
       <c r="C145" s="9"/>
-      <c r="D145" s="29"/>
+      <c r="D145" s="28"/>
       <c r="E145" s="10"/>
       <c r="F145" s="10"/>
       <c r="G145" s="10"/>
       <c r="H145" s="11"/>
       <c r="I145" s="11"/>
-      <c r="J145" s="8"/>
-    </row>
-    <row r="146" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A146" s="8"/>
+    </row>
+    <row r="146" spans="2:9" ht="15.75" customHeight="1">
       <c r="B146" s="9"/>
       <c r="C146" s="9"/>
-      <c r="D146" s="29"/>
+      <c r="D146" s="28"/>
       <c r="E146" s="10"/>
       <c r="F146" s="10"/>
       <c r="G146" s="10"/>
       <c r="H146" s="11"/>
       <c r="I146" s="11"/>
-      <c r="J146" s="8"/>
-    </row>
-    <row r="147" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A147" s="8"/>
+    </row>
+    <row r="147" spans="2:9" ht="15.75" customHeight="1">
       <c r="B147" s="9"/>
       <c r="C147" s="9"/>
-      <c r="D147" s="29"/>
+      <c r="D147" s="28"/>
       <c r="E147" s="10"/>
       <c r="F147" s="10"/>
       <c r="G147" s="10"/>
       <c r="H147" s="11"/>
       <c r="I147" s="11"/>
-      <c r="J147" s="8"/>
-    </row>
-    <row r="148" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A148" s="8"/>
+    </row>
+    <row r="148" spans="2:9" ht="15.75" customHeight="1">
       <c r="B148" s="9"/>
       <c r="C148" s="9"/>
-      <c r="D148" s="29"/>
+      <c r="D148" s="28"/>
       <c r="E148" s="10"/>
       <c r="F148" s="10"/>
       <c r="G148" s="10"/>
       <c r="H148" s="11"/>
       <c r="I148" s="11"/>
-      <c r="J148" s="8"/>
-    </row>
-    <row r="149" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A149" s="8"/>
+    </row>
+    <row r="149" spans="2:9" ht="15.75" customHeight="1">
       <c r="B149" s="9"/>
       <c r="C149" s="9"/>
-      <c r="D149" s="29"/>
+      <c r="D149" s="28"/>
       <c r="E149" s="10"/>
       <c r="F149" s="10"/>
       <c r="G149" s="10"/>
       <c r="H149" s="11"/>
       <c r="I149" s="11"/>
-      <c r="J149" s="8"/>
-    </row>
-    <row r="150" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A150" s="8"/>
+    </row>
+    <row r="150" spans="2:9" ht="15.75" customHeight="1">
       <c r="B150" s="9"/>
       <c r="C150" s="9"/>
-      <c r="D150" s="29"/>
+      <c r="D150" s="28"/>
       <c r="E150" s="10"/>
       <c r="F150" s="10"/>
       <c r="G150" s="10"/>
       <c r="H150" s="11"/>
       <c r="I150" s="11"/>
-      <c r="J150" s="8"/>
-    </row>
-    <row r="151" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A151" s="8"/>
-      <c r="B151" s="9"/>
-      <c r="C151" s="9"/>
-      <c r="D151" s="29"/>
-      <c r="E151" s="10"/>
-      <c r="F151" s="10"/>
-      <c r="G151" s="10"/>
-      <c r="H151" s="11"/>
-      <c r="I151" s="11"/>
-      <c r="J151" s="8"/>
-    </row>
-    <row r="152" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A152" s="8"/>
-      <c r="B152" s="9"/>
-      <c r="C152" s="9"/>
-      <c r="D152" s="29"/>
-      <c r="E152" s="10"/>
-      <c r="F152" s="10"/>
-      <c r="G152" s="10"/>
-      <c r="H152" s="11"/>
-      <c r="I152" s="11"/>
-      <c r="J152" s="8"/>
-    </row>
-    <row r="153" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A153" s="8"/>
-      <c r="B153" s="9"/>
-      <c r="C153" s="9"/>
-      <c r="D153" s="29"/>
-      <c r="E153" s="10"/>
-      <c r="F153" s="10"/>
-      <c r="G153" s="10"/>
-      <c r="H153" s="11"/>
-      <c r="I153" s="11"/>
-      <c r="J153" s="8"/>
-    </row>
-    <row r="154" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A154" s="8"/>
-      <c r="B154" s="9"/>
-      <c r="C154" s="9"/>
-      <c r="D154" s="29"/>
-      <c r="E154" s="10"/>
-      <c r="F154" s="10"/>
-      <c r="G154" s="10"/>
-      <c r="H154" s="11"/>
-      <c r="I154" s="11"/>
-      <c r="J154" s="8"/>
-    </row>
-    <row r="155" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A155" s="8"/>
-      <c r="B155" s="9"/>
-      <c r="C155" s="9"/>
-      <c r="D155" s="29"/>
-      <c r="E155" s="10"/>
-      <c r="F155" s="10"/>
-      <c r="G155" s="10"/>
-      <c r="H155" s="11"/>
-      <c r="I155" s="11"/>
-      <c r="J155" s="8"/>
-    </row>
-    <row r="156" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A156" s="8"/>
-      <c r="B156" s="9"/>
-      <c r="C156" s="9"/>
-      <c r="D156" s="29"/>
-      <c r="E156" s="10"/>
-      <c r="F156" s="10"/>
-      <c r="G156" s="10"/>
-      <c r="H156" s="11"/>
-      <c r="I156" s="11"/>
-      <c r="J156" s="8"/>
-    </row>
-    <row r="157" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A157" s="8"/>
-      <c r="B157" s="9"/>
-      <c r="C157" s="9"/>
-      <c r="D157" s="29"/>
-      <c r="E157" s="10"/>
-      <c r="F157" s="10"/>
-      <c r="G157" s="10"/>
-      <c r="H157" s="11"/>
-      <c r="I157" s="11"/>
-      <c r="J157" s="8"/>
-    </row>
-    <row r="158" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A158" s="8"/>
-      <c r="B158" s="9"/>
-      <c r="C158" s="9"/>
-      <c r="D158" s="29"/>
-      <c r="E158" s="10"/>
-      <c r="F158" s="10"/>
-      <c r="G158" s="10"/>
-      <c r="H158" s="11"/>
-      <c r="I158" s="11"/>
-      <c r="J158" s="8"/>
-    </row>
-    <row r="159" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A159" s="8"/>
-      <c r="B159" s="9"/>
-      <c r="C159" s="9"/>
-      <c r="D159" s="29"/>
-      <c r="E159" s="10"/>
-      <c r="F159" s="10"/>
-      <c r="G159" s="10"/>
-      <c r="H159" s="11"/>
-      <c r="I159" s="11"/>
-      <c r="J159" s="8"/>
-    </row>
-    <row r="160" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A160" s="8"/>
-      <c r="B160" s="9"/>
-      <c r="C160" s="9"/>
-      <c r="D160" s="29"/>
-      <c r="E160" s="10"/>
-      <c r="F160" s="10"/>
-      <c r="G160" s="10"/>
-      <c r="H160" s="11"/>
-      <c r="I160" s="11"/>
-      <c r="J160" s="8"/>
-    </row>
-    <row r="161" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A161" s="8"/>
-      <c r="B161" s="9"/>
-      <c r="C161" s="9"/>
-      <c r="D161" s="29"/>
-      <c r="E161" s="10"/>
-      <c r="F161" s="10"/>
-      <c r="G161" s="10"/>
-      <c r="H161" s="11"/>
-      <c r="I161" s="11"/>
-      <c r="J161" s="8"/>
-    </row>
-    <row r="162" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A162" s="8"/>
-      <c r="B162" s="9"/>
-      <c r="C162" s="9"/>
-      <c r="D162" s="29"/>
-      <c r="E162" s="10"/>
-      <c r="F162" s="10"/>
-      <c r="G162" s="10"/>
-      <c r="H162" s="11"/>
-      <c r="I162" s="11"/>
-      <c r="J162" s="8"/>
-    </row>
-    <row r="163" spans="1:10" ht="15.75" customHeight="1">
-      <c r="B163" s="9"/>
-      <c r="C163" s="9"/>
-      <c r="D163" s="29"/>
-      <c r="E163" s="10"/>
-      <c r="F163" s="10"/>
-      <c r="G163" s="10"/>
-      <c r="H163" s="11"/>
-      <c r="I163" s="11"/>
-    </row>
-    <row r="164" spans="1:10" ht="15.75" customHeight="1">
-      <c r="B164" s="9"/>
-      <c r="C164" s="9"/>
-      <c r="D164" s="29"/>
-      <c r="E164" s="10"/>
-      <c r="F164" s="10"/>
-      <c r="G164" s="10"/>
-      <c r="H164" s="11"/>
-      <c r="I164" s="11"/>
-    </row>
-    <row r="165" spans="1:10" ht="15.75" customHeight="1">
-      <c r="B165" s="9"/>
-      <c r="C165" s="9"/>
-      <c r="D165" s="29"/>
-      <c r="E165" s="10"/>
-      <c r="F165" s="10"/>
-      <c r="G165" s="10"/>
-      <c r="H165" s="11"/>
-      <c r="I165" s="11"/>
-    </row>
-    <row r="166" spans="1:10" ht="15.75" customHeight="1">
-      <c r="B166" s="9"/>
-      <c r="C166" s="9"/>
-      <c r="D166" s="29"/>
-      <c r="E166" s="10"/>
-      <c r="F166" s="10"/>
-      <c r="G166" s="10"/>
-      <c r="H166" s="11"/>
-      <c r="I166" s="11"/>
-    </row>
-    <row r="167" spans="1:10" ht="15.75" customHeight="1">
-      <c r="B167" s="9"/>
-      <c r="C167" s="9"/>
-      <c r="D167" s="29"/>
-      <c r="E167" s="10"/>
-      <c r="F167" s="10"/>
-      <c r="G167" s="10"/>
-      <c r="H167" s="11"/>
-      <c r="I167" s="11"/>
-    </row>
-    <row r="168" spans="1:10" ht="15.75" customHeight="1">
-      <c r="B168" s="9"/>
-      <c r="C168" s="9"/>
-      <c r="D168" s="29"/>
-      <c r="E168" s="10"/>
-      <c r="F168" s="10"/>
-      <c r="G168" s="10"/>
-      <c r="H168" s="11"/>
-      <c r="I168" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B47:I47"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E26" r:id="rId1" xr:uid="{6B1FB2A7-612F-4666-9A70-E34BE6807D88}"/>
+    <hyperlink ref="E11" r:id="rId2" xr:uid="{1806A520-6A46-4A08-BBC6-9B40DA73A707}"/>
+    <hyperlink ref="E12" r:id="rId3" xr:uid="{7A5205EC-9E65-48C0-9CA3-B42AE9DDCFE9}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
-  <tableParts count="7">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
+  <tableParts count="3">
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
-    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4102,33 +3279,33 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.6796875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="3" width="9.109375" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" customWidth="1"/>
-    <col min="8" max="8" width="22.109375" customWidth="1"/>
-    <col min="9" max="9" width="9.109375" customWidth="1"/>
-    <col min="10" max="10" width="5.109375" customWidth="1"/>
+    <col min="1" max="1" width="5.08984375" customWidth="1"/>
+    <col min="2" max="3" width="9.08984375" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" customWidth="1"/>
+    <col min="5" max="5" width="18.08984375" customWidth="1"/>
+    <col min="6" max="6" width="14.08984375" customWidth="1"/>
+    <col min="7" max="7" width="12.86328125" customWidth="1"/>
+    <col min="8" max="8" width="22.08984375" customWidth="1"/>
+    <col min="9" max="9" width="9.08984375" customWidth="1"/>
+    <col min="10" max="10" width="5.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="70.5" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="48" t="s">
-        <v>128</v>
-      </c>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
+        <v>65</v>
+      </c>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="30"/>
+      <c r="G1" s="29"/>
       <c r="H1" s="49">
         <v>2016</v>
       </c>
-      <c r="I1" s="46"/>
+      <c r="I1" s="47"/>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="12" customHeight="1">
@@ -4145,293 +3322,293 @@
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1">
       <c r="A3" s="4"/>
-      <c r="B3" s="47" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
+      <c r="B3" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="24" customHeight="1">
       <c r="A4" s="6"/>
-      <c r="B4" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F4" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="G4" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="I4" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="J4" s="33"/>
+      <c r="B4" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="32"/>
     </row>
     <row r="5" spans="1:10" ht="21" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="34">
+      <c r="B5" s="33">
         <v>36773</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="34">
         <f t="shared" ref="C5:C19" si="0">B5</f>
         <v>36773</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="35">
         <v>0.54166666666666663</v>
       </c>
-      <c r="E5" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="F5" s="37" t="s">
-        <v>137</v>
-      </c>
-      <c r="G5" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="H5" s="38"/>
-      <c r="I5" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="J5" s="40"/>
+      <c r="E5" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="37"/>
+      <c r="I5" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="J5" s="39"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
       <c r="A6" s="8"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="35">
+      <c r="B6" s="33"/>
+      <c r="C6" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D6" s="36"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="39"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="8"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="35">
+      <c r="B7" s="33"/>
+      <c r="C7" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="40"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="39"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
       <c r="A8" s="8"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="35">
+      <c r="B8" s="33"/>
+      <c r="C8" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D8" s="36"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="40"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="39"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
       <c r="A9" s="8"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="35">
+      <c r="B9" s="33"/>
+      <c r="C9" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="40"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="39"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
       <c r="A10" s="8"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="35">
+      <c r="B10" s="33"/>
+      <c r="C10" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D10" s="36"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="40"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="39"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
       <c r="A11" s="8"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="35">
+      <c r="B11" s="33"/>
+      <c r="C11" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="40"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="39"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
       <c r="A12" s="8"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="35">
+      <c r="B12" s="33"/>
+      <c r="C12" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="39"/>
     </row>
     <row r="13" spans="1:10" ht="21" customHeight="1">
       <c r="A13" s="8"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="35">
+      <c r="B13" s="33"/>
+      <c r="C13" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="40"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="39"/>
     </row>
     <row r="14" spans="1:10" ht="24" customHeight="1">
       <c r="A14" s="8"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="35">
+      <c r="B14" s="40"/>
+      <c r="C14" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
       <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:10" ht="30" customHeight="1">
       <c r="A15" s="4"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="35">
+      <c r="B15" s="42"/>
+      <c r="C15" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="1:10" ht="24" customHeight="1">
       <c r="A16" s="6"/>
-      <c r="B16" s="44"/>
-      <c r="C16" s="35">
+      <c r="B16" s="43"/>
+      <c r="C16" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="45"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
       <c r="J16" s="6"/>
     </row>
     <row r="17" spans="1:10" ht="21" customHeight="1">
       <c r="A17" s="8"/>
-      <c r="B17" s="41"/>
-      <c r="C17" s="35">
+      <c r="B17" s="40"/>
+      <c r="C17" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
       <c r="G17" s="11"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
+      <c r="H17" s="40"/>
+      <c r="I17" s="40"/>
       <c r="J17" s="8"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
       <c r="A18" s="8"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="35">
+      <c r="B18" s="40"/>
+      <c r="C18" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
+      <c r="H18" s="40"/>
+      <c r="I18" s="40"/>
       <c r="J18" s="8"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
       <c r="A19" s="8"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="35">
+      <c r="B19" s="40"/>
+      <c r="C19" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
       <c r="J19" s="8"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
       <c r="A20" s="8"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
       <c r="J20" s="8"/>
     </row>
   </sheetData>
